--- a/412-sfe-lot-3-serafin/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/412-sfe-lot-3-serafin/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T14:20:20+00:00</t>
+    <t>2026-01-16T16:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
